--- a/input_EPMTPQ.xlsx
+++ b/input_EPMTPQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Estefano/tesis_master_opti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40CC783-594C-E04B-A9C4-284DDC902D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5300B94-4985-6447-B580-172754D464A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="809" xr2:uid="{9DE4DB72-F9E9-1A41-B7BB-B7A3D9A7752B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="809" activeTab="7" xr2:uid="{9DE4DB72-F9E9-1A41-B7BB-B7A3D9A7752B}"/>
   </bookViews>
   <sheets>
     <sheet name="Buses" sheetId="1" r:id="rId1"/>
@@ -99,9 +99,6 @@
     <t>Enchufable</t>
   </si>
   <si>
-    <t>Rápido</t>
-  </si>
-  <si>
     <t>Terminal de transferencia</t>
   </si>
   <si>
@@ -260,6 +257,9 @@
   </si>
   <si>
     <t>Ruminahui</t>
+  </si>
+  <si>
+    <t>Rapido</t>
   </si>
 </sst>
 </file>
@@ -764,34 +764,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -838,7 +838,7 @@
         <v>360</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4">
         <v>16</v>
@@ -875,7 +875,7 @@
         <v>450</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
@@ -912,10 +912,10 @@
         <v>250</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="4">
         <v>16</v>
@@ -952,10 +952,10 @@
         <v>320</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="G6" s="4">
         <v>16</v>
@@ -1212,7 +1212,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3" t="str">
         <f>IF(Buses!L2&lt;&gt;"",Buses!L2,"")</f>
@@ -1395,7 +1395,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3" t="str">
         <f>IF(Buses!L2&lt;&gt;"",Buses!L2,"")</f>
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>10</v>
@@ -1877,30 +1877,30 @@
         <v>7</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4">
         <v>10000</v>
@@ -1909,7 +1909,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -1939,7 +1939,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -1951,16 +1951,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E4" s="4">
         <v>110000</v>
@@ -1969,14 +1969,14 @@
         <v>120</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="str">
         <f>_xlfn.CONCAT(A4,"_",IF(B4="Deposito","CD",IF(B4="Terminal de transferencia","CT",IF(B4="Parada de bus","CP","Sin ubicacion"))),"_",IF(C4="Enchufable","Ench",IF(C4="Pantografo","Pant","Sin conexion")),IF(D4&lt;&gt;"",_xlfn.CONCAT("_",D4),""))</f>
-        <v>3_Individual_CT_Ench_Rápido</v>
+        <v>3_Individual_CT_Ench_Rapido</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -1999,27 +1999,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>800000</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2043,7 +2043,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="str">
         <f>IF(Cargadores!I2&lt;&gt;"",Cargadores!I2,"")</f>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="D1" s="7" t="str">
         <f>IF(Cargadores!I4&lt;&gt;"",Cargadores!I4,"")</f>
-        <v>3_Individual_CT_Ench_Rápido</v>
+        <v>3_Individual_CT_Ench_Rapido</v>
       </c>
       <c r="F1" s="2" t="str">
         <f>IF(Cargadores!I5&lt;&gt;"",Cargadores!I5,"")</f>
@@ -2418,36 +2418,36 @@
   <sheetData>
     <row r="1" spans="1:14" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="4">
         <v>34.61</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4">
         <v>30.7</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4">
         <v>14.45</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="4">
         <v>13.46</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4">
         <v>9.7100000000000009</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4">
         <v>9.65</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>11.21</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="4">
         <v>14.68</v>
@@ -2697,7 +2697,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="str">
         <f>IF(Buses!L2&lt;&gt;"",Buses!L2,"")</f>

--- a/input_EPMTPQ.xlsx
+++ b/input_EPMTPQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Estefano/tesis_master_opti/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC01\Documents\tesis_master_opti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5300B94-4985-6447-B580-172754D464A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAEEC43-7DC2-464C-8E53-AEEA0253FD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="809" activeTab="7" xr2:uid="{9DE4DB72-F9E9-1A41-B7BB-B7A3D9A7752B}"/>
+    <workbookView xWindow="8295" yWindow="360" windowWidth="29250" windowHeight="13890" tabRatio="809" activeTab="7" xr2:uid="{9DE4DB72-F9E9-1A41-B7BB-B7A3D9A7752B}"/>
   </bookViews>
   <sheets>
     <sheet name="Buses" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{59E87DFE-8D24-0F46-9F50-19BCE2900944}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Precio de venta de un bus diesel de edad 0</t>
       </text>
@@ -187,9 +187,6 @@
     <t>Cisne-Zabala</t>
   </si>
   <si>
-    <t>Llano Grande</t>
-  </si>
-  <si>
     <t>Cotocollao</t>
   </si>
   <si>
@@ -253,13 +250,16 @@
     <t>Inter-terminales_CL</t>
   </si>
   <si>
-    <t>Comite del Pueblo</t>
-  </si>
-  <si>
     <t>Ruminahui</t>
   </si>
   <si>
     <t>Rapido</t>
+  </si>
+  <si>
+    <t>Llano_Grande</t>
+  </si>
+  <si>
+    <t>Comité_del_Pueblo</t>
   </si>
 </sst>
 </file>
@@ -744,19 +744,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D07D0FC-A55A-A84B-B1CD-1117AD658092}">
   <dimension ref="A1:L80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="4"/>
-    <col min="5" max="5" width="13.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="4" customWidth="1"/>
-    <col min="7" max="9" width="10.83203125" style="4" customWidth="1"/>
+    <col min="1" max="4" width="10.875" style="4"/>
+    <col min="5" max="5" width="13.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="4" customWidth="1"/>
+    <col min="7" max="9" width="10.875" style="4" customWidth="1"/>
     <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="4"/>
-    <col min="12" max="12" width="19.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="4"/>
+    <col min="11" max="11" width="10.875" style="4"/>
+    <col min="12" max="12" width="19.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="67" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="66.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -764,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>4</v>
@@ -785,7 +785,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>8</v>
@@ -794,7 +794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -824,7 +824,7 @@
         <v>1_Diesel_12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -861,7 +861,7 @@
         <v>2_EB_12_360_CD</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -898,7 +898,7 @@
         <v>3_EB_12_450_CD</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -938,7 +938,7 @@
         <v>4_EB_12_250_CD+CT</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -978,226 +978,226 @@
         <v>5_EB_12_320_CD+CT</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L11" s="12"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L12" s="12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L33" s="12"/>
     </row>
-    <row r="34" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L34" s="12"/>
     </row>
-    <row r="35" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L35" s="12"/>
     </row>
-    <row r="36" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L36" s="12"/>
     </row>
-    <row r="37" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L37" s="12"/>
     </row>
-    <row r="38" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L38" s="12"/>
     </row>
-    <row r="39" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L39" s="12"/>
     </row>
-    <row r="40" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L40" s="12"/>
     </row>
-    <row r="41" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L41" s="12"/>
     </row>
-    <row r="42" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L42" s="12"/>
     </row>
-    <row r="43" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L43" s="12"/>
     </row>
-    <row r="44" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L44" s="12"/>
     </row>
-    <row r="45" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L45" s="12"/>
     </row>
-    <row r="46" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L46" s="12"/>
     </row>
-    <row r="47" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L47" s="12"/>
     </row>
-    <row r="48" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L48" s="12"/>
     </row>
-    <row r="49" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L50" s="12"/>
     </row>
-    <row r="51" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L53" s="12"/>
     </row>
-    <row r="54" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L54" s="12"/>
     </row>
-    <row r="55" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L55" s="12"/>
     </row>
-    <row r="56" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L56" s="12"/>
     </row>
-    <row r="57" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L57" s="12"/>
     </row>
-    <row r="58" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L58" s="12"/>
     </row>
-    <row r="59" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L59" s="12"/>
     </row>
-    <row r="60" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L60" s="12"/>
     </row>
-    <row r="61" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L62" s="12"/>
     </row>
-    <row r="63" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L63" s="12"/>
     </row>
-    <row r="64" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L64" s="12"/>
     </row>
-    <row r="65" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L65" s="12"/>
     </row>
-    <row r="66" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L66" s="12"/>
     </row>
-    <row r="67" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L67" s="12"/>
     </row>
-    <row r="68" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L68" s="12"/>
     </row>
-    <row r="69" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L69" s="12"/>
     </row>
-    <row r="70" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L70" s="12"/>
     </row>
-    <row r="71" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L71" s="12"/>
     </row>
-    <row r="72" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L72" s="12"/>
     </row>
-    <row r="73" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L73" s="12"/>
     </row>
-    <row r="74" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L74" s="12"/>
     </row>
-    <row r="75" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L75" s="12"/>
     </row>
-    <row r="76" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L76" s="12"/>
     </row>
-    <row r="77" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L77" s="12"/>
     </row>
-    <row r="78" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L78" s="12"/>
     </row>
-    <row r="79" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L79" s="12"/>
     </row>
-    <row r="80" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L80" s="12"/>
     </row>
   </sheetData>
@@ -1208,9 +1208,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2034B225-C564-F54A-8C16-441A2AD33684}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1235,12 +1235,12 @@
         <v>5_EB_12_320_CD+CT</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1256,18 +1256,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1307,12 +1307,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1336,17 +1336,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1370,17 +1370,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G25" s="8"/>
     </row>
   </sheetData>
@@ -1391,9 +1391,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7790FFC7-7D4C-BC4E-82E6-9C1F94B41064}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>5_EB_12_320_CD+CT</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1847,20 +1847,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3222A92-7CEF-E147-8210-784379CE4856}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="4"/>
-    <col min="2" max="2" width="30.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="10.875" style="4"/>
+    <col min="2" max="2" width="30.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="4"/>
     <col min="4" max="4" width="22" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="4"/>
-    <col min="7" max="7" width="12.1640625" style="12" customWidth="1"/>
+    <col min="5" max="6" width="10.875" style="4"/>
+    <col min="7" max="7" width="12.125" style="12" customWidth="1"/>
     <col min="8" max="8" width="10" style="12" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="4"/>
+    <col min="9" max="9" width="32.625" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1889,18 +1889,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="4">
         <v>10000</v>
@@ -1909,7 +1909,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
@@ -1919,7 +1919,7 @@
         <v>1_Pila_CD+CT_Ench_Lento_o_Rapido</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -1949,9 +1949,9 @@
         <v>2_Inidividual_CD_Ench_Lento</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
@@ -1960,7 +1960,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" s="4">
         <v>110000</v>
@@ -1979,7 +1979,7 @@
         <v>3_Individual_CT_Ench_Rapido</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G8" s="4"/>
     </row>
   </sheetData>
@@ -1990,14 +1990,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4BE54C-254B-40E9-9936-1D397B2AD6C5}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -2005,21 +2005,21 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>800000</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2033,15 +2033,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BD560C-3450-7149-B4B7-34674DBD5BE4}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="113.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -2078,13 +2078,13 @@
         <v/>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(Buses!L2&lt;&gt;"",Buses!L2,"")</f>
         <v>1_Diesel_12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>IF(Buses!L3&lt;&gt;"",Buses!L3,"")</f>
         <v>2_EB_12_360_CD</v>
@@ -2096,7 +2096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(Buses!L4&lt;&gt;"",Buses!L4,"")</f>
         <v>3_EB_12_450_CD</v>
@@ -2108,7 +2108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(Buses!L5&lt;&gt;"",Buses!L5,"")</f>
         <v>4_EB_12_250_CD+CT</v>
@@ -2123,7 +2123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(Buses!L6&lt;&gt;"",Buses!L6,"")</f>
         <v>5_EB_12_320_CD+CT</v>
@@ -2138,265 +2138,265 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>IF(Buses!L7&lt;&gt;"",Buses!L7,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>IF(Buses!L8&lt;&gt;"",Buses!L8,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>IF(Buses!L9&lt;&gt;"",Buses!L9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>IF(Buses!L10&lt;&gt;"",Buses!L10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>IF(Buses!L11&lt;&gt;"",Buses!L11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>IF(Buses!L12&lt;&gt;"",Buses!L12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>IF(Buses!L13&lt;&gt;"",Buses!L13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f>IF(Buses!L14&lt;&gt;"",Buses!L14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>IF(Buses!L15&lt;&gt;"",Buses!L15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f>IF(Buses!L16&lt;&gt;"",Buses!L16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>IF(Buses!L17&lt;&gt;"",Buses!L17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>IF(Buses!L18&lt;&gt;"",Buses!L18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>IF(Buses!L19&lt;&gt;"",Buses!L19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>IF(Buses!L20&lt;&gt;"",Buses!L20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>IF(Buses!L21&lt;&gt;"",Buses!L21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>IF(Buses!L22&lt;&gt;"",Buses!L22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>IF(Buses!L23&lt;&gt;"",Buses!L23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>IF(Buses!L24&lt;&gt;"",Buses!L24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(Buses!L25&lt;&gt;"",Buses!L25,"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>IF(Buses!L26&lt;&gt;"",Buses!L26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>IF(Buses!L27&lt;&gt;"",Buses!L27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>IF(Buses!L28&lt;&gt;"",Buses!L28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f>IF(Buses!L29&lt;&gt;"",Buses!L29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>IF(Buses!L30&lt;&gt;"",Buses!L30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>IF(Buses!L31&lt;&gt;"",Buses!L31,"")</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>IF(Buses!L32&lt;&gt;"",Buses!L32,"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>IF(Buses!L33&lt;&gt;"",Buses!L33,"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>IF(Buses!L34&lt;&gt;"",Buses!L34,"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>IF(Buses!L35&lt;&gt;"",Buses!L35,"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>IF(Buses!L36&lt;&gt;"",Buses!L36,"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f>IF(Buses!L37&lt;&gt;"",Buses!L37,"")</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>IF(Buses!L38&lt;&gt;"",Buses!L38,"")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>IF(Buses!L39&lt;&gt;"",Buses!L39,"")</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>IF(Buses!L40&lt;&gt;"",Buses!L40,"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>IF(Buses!L41&lt;&gt;"",Buses!L41,"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f>IF(Buses!L42&lt;&gt;"",Buses!L42,"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>IF(Buses!L43&lt;&gt;"",Buses!L43,"")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(Buses!L44&lt;&gt;"",Buses!L44,"")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f>IF(Buses!L45&lt;&gt;"",Buses!L45,"")</f>
         <v/>
@@ -2410,13 +2410,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA787025-24AE-3B4E-A437-559C4DA77465}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="4"/>
+    <col min="2" max="16384" width="10.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -2424,28 +2424,28 @@
         <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>33</v>
       </c>
@@ -2474,9 +2474,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4">
         <v>30.7</v>
@@ -2503,9 +2503,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4">
         <v>14.45</v>
@@ -2534,9 +2534,9 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="4">
         <v>13.46</v>
@@ -2563,9 +2563,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
         <v>9.7100000000000009</v>
@@ -2592,9 +2592,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4">
         <v>9.65</v>
@@ -2621,9 +2621,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" s="4">
         <v>11.21</v>
@@ -2650,9 +2650,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4">
         <v>14.68</v>
@@ -2687,15 +2687,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2EE435-E53E-D845-B842-73C422058DA6}">
   <dimension ref="A1:L55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="113.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>5_EB_12_320_CD+CT</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(Rutas!A2&lt;&gt;"",Rutas!A2,"")</f>
         <v>Cisne-Zabala</v>
@@ -2743,10 +2743,10 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>IF(Rutas!A3&lt;&gt;"",Rutas!A3,"")</f>
-        <v>Llano Grande</v>
+        <v>Llano_Grande</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2770,10 +2770,10 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(Rutas!A4&lt;&gt;"",Rutas!A4,"")</f>
-        <v>Comite del Pueblo</v>
+        <v>Comité_del_Pueblo</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2797,7 +2797,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(Rutas!A5&lt;&gt;"",Rutas!A5,"")</f>
         <v>Cotocollao</v>
@@ -2824,7 +2824,7 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(Rutas!A6&lt;&gt;"",Rutas!A6,"")</f>
         <v>Kennedy</v>
@@ -2851,7 +2851,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>IF(Rutas!A7&lt;&gt;"",Rutas!A7,"")</f>
         <v>Laureles</v>
@@ -2878,7 +2878,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>IF(Rutas!A8&lt;&gt;"",Rutas!A8,"")</f>
         <v>Ruminahui</v>
@@ -2905,7 +2905,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>IF(Rutas!A9&lt;&gt;"",Rutas!A9,"")</f>
         <v>Inter-terminales_CL</v>
@@ -2932,7 +2932,7 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="1"/>
       <c r="D10" s="4"/>
@@ -2945,7 +2945,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="1"/>
       <c r="D11" s="4"/>
@@ -2958,7 +2958,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2971,7 +2971,7 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -2984,7 +2984,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2997,7 +2997,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3010,7 +3010,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3023,7 +3023,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3036,7 +3036,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3049,7 +3049,7 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3062,7 +3062,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -3075,7 +3075,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3088,7 +3088,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -3100,7 +3100,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -3113,7 +3113,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -3126,7 +3126,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -3139,7 +3139,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -3152,7 +3152,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -3165,7 +3165,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -3178,7 +3178,7 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -3191,7 +3191,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -3204,7 +3204,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -3217,7 +3217,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -3230,7 +3230,7 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -3243,7 +3243,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -3256,7 +3256,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -3269,7 +3269,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -3282,7 +3282,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -3295,7 +3295,7 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3308,7 +3308,7 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -3321,7 +3321,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -3334,7 +3334,7 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -3347,7 +3347,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -3360,7 +3360,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -3373,7 +3373,7 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -3386,7 +3386,7 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -3399,7 +3399,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -3412,7 +3412,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3425,7 +3425,7 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3438,7 +3438,7 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3451,7 +3451,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3464,7 +3464,7 @@
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3477,7 +3477,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3490,7 +3490,7 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3503,7 +3503,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
       <c r="D54" s="1"/>
       <c r="F54" s="1"/>
@@ -3512,7 +3512,7 @@
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
       <c r="D55" s="1"/>
       <c r="F55" s="1"/>
